--- a/data/trans_dic/IP16B01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,87</t>
+          <t>0,0; 10,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,55; 100,0</t>
+          <t>83,98; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,94; 93,14</t>
+          <t>51,78; 93,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,11; 96,78</t>
+          <t>75,23; 96,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,92; 93,31</t>
+          <t>44,77; 92,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83,65; 98,25</t>
+          <t>84,95; 98,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,85; 89,83</t>
+          <t>60,28; 90,36</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,01; 83,41</t>
+          <t>55,42; 85,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,25; 97,69</t>
+          <t>78,82; 97,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,78; 100,0</t>
+          <t>85,72; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,35; 97,6</t>
+          <t>79,94; 97,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,98; 91,48</t>
+          <t>73,27; 91,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,81; 96,14</t>
+          <t>83,64; 96,21</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,41; 85,56</t>
+          <t>57,64; 87,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,47; 90,1</t>
+          <t>56,2; 89,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,04; 100,0</t>
+          <t>85,1; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,51; 100,0</t>
+          <t>75,28; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,15; 92,33</t>
+          <t>75,36; 92,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,62; 92,35</t>
+          <t>72,3; 92,56</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,19; 94,75</t>
+          <t>70,52; 94,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,47; 89,12</t>
+          <t>56,02; 88,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,55; 97,76</t>
+          <t>79,05; 97,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,57; 96,22</t>
+          <t>67,31; 96,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,67; 94,56</t>
+          <t>78,49; 94,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,61; 89,82</t>
+          <t>68,99; 90,8</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,19; 88,06</t>
+          <t>75,35; 88,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,73; 88,63</t>
+          <t>73,88; 87,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,68; 91,27</t>
+          <t>83,55; 91,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,18; 89,58</t>
+          <t>79,58; 89,15</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22771</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11095</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19322</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8152</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>42093</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>19246</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3586</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19724; 23486</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7445; 13513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16214; 20844</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4736; 9834</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2936</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>38261; 44305</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>15045; 22553</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17329</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22813</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23391</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>39229</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>46204</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3192</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13361; 20604</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19534; 24207</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>19264; 22472</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20693; 25260</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3220</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>34130; 42670</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>42377; 48743</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14427</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24429</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12979</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>39875</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27407</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12146; 18437</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10574; 16871</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21839; 25664</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10269; 13642</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>35222; 43231</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23466; 30041</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25327</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14082</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26802</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14458</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>52129</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28540</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20831; 27911</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10320; 16367</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>23131; 28603</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11225; 16046</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>46148; 55442</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24213; 31868</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80874</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62418</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92453</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58981</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>173326</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>121399</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4707</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73996; 86422</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56439; 67099</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>87123; 96011</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53488; 62610</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5026</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>164724; 179957</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>113939; 127644</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Habitat-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,93</t>
+          <t>0,0; 11,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,98; 100,0</t>
+          <t>83,9; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,78; 93,99</t>
+          <t>52,61; 93,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,23; 96,72</t>
+          <t>72,9; 96,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 92,95</t>
+          <t>49,19; 93,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,95; 98,37</t>
+          <t>84,91; 98,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,28; 90,36</t>
+          <t>58,14; 89,84</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,42; 85,46</t>
+          <t>55,52; 85,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,82; 97,68</t>
+          <t>78,71; 97,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,72; 100,0</t>
+          <t>86,86; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,94; 97,59</t>
+          <t>79,05; 97,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>73,27; 91,6</t>
+          <t>73,85; 91,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,64; 96,21</t>
+          <t>82,17; 96,23</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,64; 87,49</t>
+          <t>57,12; 87,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,2; 89,67</t>
+          <t>57,73; 89,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,1; 100,0</t>
+          <t>85,04; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,28; 100,0</t>
+          <t>71,54; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>75,36; 92,5</t>
+          <t>75,04; 92,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,3; 92,56</t>
+          <t>72,43; 92,17</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,52; 94,49</t>
+          <t>69,53; 94,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,02; 88,86</t>
+          <t>57,87; 91,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,05; 97,76</t>
+          <t>78,34; 97,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,31; 96,22</t>
+          <t>65,94; 96,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,49; 94,29</t>
+          <t>79,75; 94,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,99; 90,8</t>
+          <t>67,45; 91,18</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,35; 88,0</t>
+          <t>75,02; 87,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,88; 87,83</t>
+          <t>73,09; 87,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,55; 91,28</t>
+          <t>83,82; 91,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79,58; 89,15</t>
+          <t>79,46; 89,31</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 3849</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19724; 23486</t>
+          <t>19704; 23486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7445; 13513</t>
+          <t>7564; 13479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,27 +1437,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16214; 20844</t>
+          <t>15711; 20856</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4736; 9834</t>
+          <t>5204; 9892</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2936</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38261; 44305</t>
+          <t>38240; 44333</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15045; 22553</t>
+          <t>14511; 22423</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3192</t>
+          <t>0; 2952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13361; 20604</t>
+          <t>13385; 20685</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19534; 24207</t>
+          <t>19506; 24202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1600,27 +1600,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19264; 22472</t>
+          <t>19519; 22472</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20693; 25260</t>
+          <t>20461; 25272</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>0; 3289</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34130; 42670</t>
+          <t>34398; 42578</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42377; 48743</t>
+          <t>41633; 48756</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12146; 18437</t>
+          <t>12037; 18419</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10574; 16871</t>
+          <t>10862; 16835</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21839; 25664</t>
+          <t>21825; 25664</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10269; 13642</t>
+          <t>9760; 13642</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35222; 43231</t>
+          <t>35071; 43064</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23466; 30041</t>
+          <t>23507; 29916</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20831; 27911</t>
+          <t>20539; 27926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10320; 16367</t>
+          <t>10659; 16865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23131; 28603</t>
+          <t>22921; 28600</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11225; 16046</t>
+          <t>10996; 16042</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46148; 55442</t>
+          <t>46889; 55670</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24213; 31868</t>
+          <t>23674; 32002</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2069,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 4725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73996; 86422</t>
+          <t>73677; 86225</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56439; 67099</t>
+          <t>55837; 67045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2089,27 +2089,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>87123; 96011</t>
+          <t>87037; 95751</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53488; 62610</t>
+          <t>53546; 62516</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5026</t>
+          <t>0; 4704</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164724; 179957</t>
+          <t>165258; 180086</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>113939; 127644</t>
+          <t>113767; 127868</t>
         </is>
       </c>
     </row>
